--- a/output/pdf_financials_xlsx/FRU.xlsx
+++ b/output/pdf_financials_xlsx/FRU.xlsx
@@ -864,28 +864,28 @@
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>4.197</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>6.474</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>6.378</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>5.666</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>2.297</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>1.317</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>1.174</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>0.694</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0</v>
@@ -42700,7 +42700,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -42712,28 +42716,28 @@
         </is>
       </c>
       <c r="G373" s="5" t="n">
-        <v>-4.197</v>
+        <v>4.197</v>
       </c>
       <c r="H373" s="5" t="n">
-        <v>-6.474</v>
+        <v>6.474</v>
       </c>
       <c r="I373" s="5" t="n">
-        <v>-6.378</v>
+        <v>6.378</v>
       </c>
       <c r="J373" s="5" t="n">
-        <v>-5.666</v>
+        <v>5.666</v>
       </c>
       <c r="K373" s="5" t="n">
-        <v>-2.297</v>
+        <v>2.297</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>-1.317</v>
+        <v>1.317</v>
       </c>
       <c r="M373" s="5" t="n">
-        <v>-1.174</v>
+        <v>1.174</v>
       </c>
       <c r="N373" s="5" t="n">
-        <v>-0.694</v>
+        <v>0.694</v>
       </c>
       <c r="O373" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FRU.xlsx
+++ b/output/pdf_financials_xlsx/FRU.xlsx
@@ -2285,46 +2285,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.126</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.876</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.892</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.284</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.262</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.199</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.189</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0</v>
@@ -2395,46 +2395,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.126</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.876</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.892</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.284</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.262</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.199</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.189</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0</v>
@@ -3055,46 +3055,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.164</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.102</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.723</v>
+        <v>2.597</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.949</v>
+        <v>0.073</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.892</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>14.094</v>
+        <v>13.81</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.262</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.199</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>16.9</v>
+        <v>14.711</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>22.433</v>
+        <v>21.909</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>22.433</v>
+        <v>21.909</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>4.385</v>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -20756,7 +20756,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">

--- a/output/pdf_financials_xlsx/FRU.xlsx
+++ b/output/pdf_financials_xlsx/FRU.xlsx
@@ -4371,22 +4371,22 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="71">
@@ -4426,22 +4426,22 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="72">
@@ -4646,22 +4646,22 @@
         <v>8.965</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>7.832</v>
+        <v>7.783</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>13.269</v>
+        <v>13.074</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>47.411</v>
+        <v>47.216</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>27.289</v>
+        <v>27.026</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>29.046</v>
+        <v>28.682</v>
       </c>
     </row>
     <row r="76">
@@ -4923,22 +4923,22 @@
         <v>0.1161867508375128</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.1540686128312299</v>
+        <v>0.1541378730333283</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.1638670835924154</v>
+        <v>0.1640859471629669</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.163025425343706</v>
+        <v>0.1632284782176331</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.163025425343706</v>
+        <v>0.1632284782176331</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.273640207703663</v>
+        <v>0.2738794180004384</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.2833099789961208</v>
+        <v>0.2836745670766947</v>
       </c>
     </row>
     <row r="81">
@@ -6429,25 +6429,25 @@
         <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.325</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.396</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.597</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0.147</v>
+        <v>0.852</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0.718</v>
+        <v>1.16</v>
       </c>
       <c r="J107" s="3" t="n">
         <v>-0.051</v>
@@ -8245,7 +8245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T429"/>
+  <dimension ref="A1:T437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9270,7 +9270,11 @@
           <t>Current portion of lease obligation (note 12)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -11702,7 +11706,11 @@
           <t>Current portion of lease obligation 263</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -13380,7 +13388,11 @@
           <t>Current portion of lease obligation (note 5)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14284,7 +14296,11 @@
           <t>Current portion of lease obligation (note 6)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -23704,7 +23720,11 @@
           <t>Deferred income tax expense (note 14)</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -25966,7 +25986,11 @@
           <t>Deferred income tax expense (note 13)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -30722,7 +30746,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -33306,7 +33334,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -33492,7 +33524,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -34562,7 +34598,11 @@
           <t>Share based compensation expense</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -34926,7 +34966,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -38864,10 +38908,8 @@
       <c r="K331" s="5" t="n">
         <v>-11.539</v>
       </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L331" s="5" t="n">
+        <v>-3.097</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
@@ -39480,10 +39522,8 @@
       <c r="K338" s="5" t="n">
         <v>90.504786</v>
       </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L338" s="5" t="n">
+        <v>110.39116</v>
       </c>
       <c r="M338" s="5" t="n">
         <v>118.162099</v>
@@ -43745,10 +43785,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K384" s="5" t="n">
+        <v>135.664</v>
       </c>
       <c r="L384" s="5" t="n">
         <v>129.968</v>
@@ -43935,10 +43973,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K386" s="5" t="n">
+        <v>0.766</v>
       </c>
       <c r="L386" s="5" t="n">
         <v>1.208</v>
@@ -44748,40 +44784,50 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Chief Executive Officer                        Chief Financial Officer</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Royalty income and working interest sales $</t>
+          <t>March</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
-      <c r="E395" s="5" t="n">
-        <v>119.965</v>
-      </c>
-      <c r="F395" s="5" t="n">
-        <v>138.155</v>
-      </c>
-      <c r="G395" s="5" t="n">
-        <v>157.91</v>
-      </c>
-      <c r="H395" s="5" t="n">
-        <v>168.134</v>
-      </c>
-      <c r="I395" s="5" t="n">
-        <v>181.578</v>
-      </c>
-      <c r="J395" s="5" t="n">
-        <v>199.85</v>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K395" s="5" t="n">
-        <v>135.664</v>
-      </c>
-      <c r="L395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.015</v>
+      </c>
+      <c r="L395" s="5" t="n">
+        <v>0.002</v>
       </c>
       <c r="M395" t="inlineStr">
         <is>
@@ -44832,12 +44878,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>CHARTERED PROFESSIONAL ACCOUNTANTS</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Gain on corporate acquisition (note 3)</t>
+          <t>March</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -44872,12 +44918,10 @@
         </is>
       </c>
       <c r="K396" s="5" t="n">
-        <v>24.34</v>
-      </c>
-      <c r="L396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.017</v>
+      </c>
+      <c r="L396" s="5" t="n">
+        <v>0.002</v>
       </c>
       <c r="M396" t="inlineStr">
         <is>
@@ -44933,14 +44977,10 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Other income (note 9)</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Gain on corporate acquisition (note 3)</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -44972,7 +45012,7 @@
         </is>
       </c>
       <c r="K397" s="5" t="n">
-        <v>0.756</v>
+        <v>24.34</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -45028,12 +45068,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Share based and other compensation (note 10)</t>
+          <t>Other income (loss) (note 9, 15)</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -45047,25 +45087,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G398" s="5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="H398" s="5" t="n">
-        <v>2.371</v>
-      </c>
-      <c r="I398" s="5" t="n">
-        <v>1.531</v>
-      </c>
-      <c r="J398" s="5" t="n">
-        <v>0.438</v>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K398" s="5" t="n">
-        <v>0.766</v>
-      </c>
-      <c r="L398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.756</v>
+      </c>
+      <c r="L398" s="5" t="n">
+        <v>-1.066</v>
       </c>
       <c r="M398" t="inlineStr">
         <is>
@@ -45116,12 +45162,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Current expense (recovery)</t>
+          <t>Loss before taxes</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -45150,16 +45196,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J399" s="5" t="n">
-        <v>22.178</v>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K399" s="5" t="n">
-        <v>-5.097</v>
-      </c>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-15.619</v>
+      </c>
+      <c r="L399" s="5" t="n">
+        <v>-14.26</v>
       </c>
       <c r="M399" t="inlineStr">
         <is>
@@ -45215,7 +45261,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Deferred expense (recovery)</t>
+          <t>Current recovery</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -45239,14 +45285,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I400" s="5" t="n">
-        <v>-3.552</v>
-      </c>
-      <c r="J400" s="5" t="n">
-        <v>0.659</v>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K400" s="5" t="n">
-        <v>-6.442</v>
+        <v>-5.097</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -45307,14 +45357,10 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) $</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Deferred recovery</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -45340,16 +45386,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J401" s="5" t="n">
-        <v>66.447</v>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K401" s="5" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.442</v>
+      </c>
+      <c r="L401" s="5" t="n">
+        <v>-3.097</v>
       </c>
       <c r="M401" t="inlineStr">
         <is>
@@ -45405,12 +45451,12 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Net income (loss) per share, basic and diluted $</t>
+          <t>Net loss and comprehensive loss $</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -45438,16 +45484,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J402" s="5" t="n">
-        <v>9.399999999999999e-07</v>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K402" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.08</v>
+      </c>
+      <c r="L402" s="5" t="n">
+        <v>-11.163</v>
       </c>
       <c r="M402" t="inlineStr">
         <is>
@@ -45498,46 +45544,54 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Depletion and depreciation</t>
+          <t>Net loss per share, basic and diluted $</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E403" s="5" t="n">
-        <v>63.06</v>
-      </c>
-      <c r="F403" s="5" t="n">
-        <v>46.132</v>
-      </c>
-      <c r="G403" s="5" t="n">
-        <v>49.251</v>
-      </c>
-      <c r="H403" s="5" t="n">
-        <v>64.57599999999999</v>
-      </c>
-      <c r="I403" s="5" t="n">
-        <v>61.32</v>
-      </c>
-      <c r="J403" s="5" t="n">
-        <v>67.145</v>
-      </c>
-      <c r="K403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K403" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="L403" s="5" t="n">
+        <v>-1e-07</v>
       </c>
       <c r="M403" t="inlineStr">
         <is>
@@ -45588,45 +45642,35 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Current expense</t>
+          <t>Royalty income and working interest sales $</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E404" s="5" t="n">
+        <v>119.965</v>
+      </c>
+      <c r="F404" s="5" t="n">
+        <v>138.155</v>
+      </c>
+      <c r="G404" s="5" t="n">
+        <v>157.91</v>
+      </c>
+      <c r="H404" s="5" t="n">
+        <v>168.134</v>
       </c>
       <c r="I404" s="5" t="n">
-        <v>23.558</v>
+        <v>181.578</v>
       </c>
       <c r="J404" s="5" t="n">
-        <v>22.178</v>
-      </c>
-      <c r="K404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>199.85</v>
+      </c>
+      <c r="K404" s="5" t="n">
+        <v>135.664</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
@@ -45682,17 +45726,17 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income $</t>
+          <t>Other income (note 9)</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -45705,22 +45749,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G405" s="5" t="n">
-        <v>55.259</v>
-      </c>
-      <c r="H405" s="5" t="n">
-        <v>46.328</v>
-      </c>
-      <c r="I405" s="5" t="n">
-        <v>57.852</v>
-      </c>
-      <c r="J405" s="5" t="n">
-        <v>66.447</v>
-      </c>
-      <c r="K405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K405" s="5" t="n">
+        <v>0.756</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
@@ -45776,19 +45826,15 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Net income per share, basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share based and other compensation (note 10)</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -45800,21 +45846,19 @@
         </is>
       </c>
       <c r="G406" s="5" t="n">
-        <v>9.200000000000001e-07</v>
+        <v>2.19</v>
       </c>
       <c r="H406" s="5" t="n">
-        <v>7.1e-07</v>
+        <v>2.371</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>8.6e-07</v>
+        <v>1.531</v>
       </c>
       <c r="J406" s="5" t="n">
-        <v>9.399999999999999e-07</v>
-      </c>
-      <c r="K406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.438</v>
+      </c>
+      <c r="K406" s="5" t="n">
+        <v>0.766</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -45870,39 +45914,45 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Share based and other compensation (note 9)</t>
+          <t>Current expense (recovery)</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
-      <c r="E407" s="5" t="n">
-        <v>3.718</v>
-      </c>
-      <c r="F407" s="5" t="n">
-        <v>3.771</v>
-      </c>
-      <c r="G407" s="5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="H407" s="5" t="n">
-        <v>2.371</v>
-      </c>
-      <c r="I407" s="5" t="n">
-        <v>1.531</v>
-      </c>
-      <c r="J407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J407" s="5" t="n">
+        <v>22.178</v>
+      </c>
+      <c r="K407" s="5" t="n">
+        <v>-5.097</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -45958,43 +46008,43 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Management fee (note 8)</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E408" s="5" t="n">
-        <v>2.018</v>
-      </c>
-      <c r="F408" s="5" t="n">
-        <v>3.016</v>
-      </c>
-      <c r="G408" s="5" t="n">
-        <v>3.401</v>
-      </c>
-      <c r="H408" s="5" t="n">
-        <v>3.808</v>
+          <t>Deferred expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I408" s="5" t="n">
-        <v>4.495</v>
-      </c>
-      <c r="J408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.552</v>
+      </c>
+      <c r="J408" s="5" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="K408" s="5" t="n">
+        <v>-6.442</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
@@ -46055,10 +46105,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Current expense (note 10)</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>Net income (loss) and comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -46074,21 +46128,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H409" s="5" t="n">
-        <v>27.792</v>
-      </c>
-      <c r="I409" s="5" t="n">
-        <v>23.558</v>
-      </c>
-      <c r="J409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J409" s="5" t="n">
+        <v>66.447</v>
+      </c>
+      <c r="K409" s="5" t="n">
+        <v>-4.08</v>
       </c>
       <c r="L409" t="inlineStr">
         <is>
@@ -46149,10 +46203,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Deferred recovery (note 10)</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>Net income (loss) per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -46168,21 +46226,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H410" s="5" t="n">
-        <v>-9.175000000000001</v>
-      </c>
-      <c r="I410" s="5" t="n">
-        <v>-3.552</v>
-      </c>
-      <c r="J410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J410" s="5" t="n">
+        <v>9.399999999999999e-07</v>
+      </c>
+      <c r="K410" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
@@ -46243,35 +46301,31 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligation (note 7)</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr"/>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depletion and depreciation</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E411" s="5" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="F411" s="5" t="n">
+        <v>46.132</v>
       </c>
       <c r="G411" s="5" t="n">
-        <v>0.344</v>
+        <v>49.251</v>
       </c>
       <c r="H411" s="5" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="I411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>64.57599999999999</v>
+      </c>
+      <c r="I411" s="5" t="n">
+        <v>61.32</v>
+      </c>
+      <c r="J411" s="5" t="n">
+        <v>67.145</v>
       </c>
       <c r="K411" t="inlineStr">
         <is>
@@ -46337,7 +46391,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Current expense (note 11)</t>
+          <t>Current expense</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
@@ -46351,21 +46405,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G412" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H412" s="5" t="n">
-        <v>27.792</v>
-      </c>
-      <c r="I412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I412" s="5" t="n">
+        <v>23.558</v>
+      </c>
+      <c r="J412" s="5" t="n">
+        <v>22.178</v>
       </c>
       <c r="K412" t="inlineStr">
         <is>
@@ -46431,10 +46485,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Deferred expense (recovery) (note 11)</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>Net income and comprehensive income $</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -46446,20 +46504,16 @@
         </is>
       </c>
       <c r="G413" s="5" t="n">
-        <v>20.47</v>
+        <v>55.259</v>
       </c>
       <c r="H413" s="5" t="n">
-        <v>-9.175000000000001</v>
-      </c>
-      <c r="I413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46.328</v>
+      </c>
+      <c r="I413" s="5" t="n">
+        <v>57.852</v>
+      </c>
+      <c r="J413" s="5" t="n">
+        <v>66.447</v>
       </c>
       <c r="K413" t="inlineStr">
         <is>
@@ -46520,38 +46574,40 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Royalty expense and mineral tax</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" s="5" t="n">
-        <v>-2.733</v>
-      </c>
-      <c r="F414" s="5" t="n">
-        <v>-4.092</v>
+          <t>Net income per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G414" s="5" t="n">
-        <v>-4.197</v>
-      </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.200000000000001e-07</v>
+      </c>
+      <c r="H414" s="5" t="n">
+        <v>7.1e-07</v>
+      </c>
+      <c r="I414" s="5" t="n">
+        <v>8.6e-07</v>
+      </c>
+      <c r="J414" s="5" t="n">
+        <v>9.399999999999999e-07</v>
       </c>
       <c r="K414" t="inlineStr">
         <is>
@@ -46612,41 +46668,29 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Other expense (note 10)</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share based and other compensation (note 9)</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" s="5" t="n">
+        <v>3.718</v>
       </c>
       <c r="F415" s="5" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.771</v>
+      </c>
+      <c r="G415" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>2.371</v>
+      </c>
+      <c r="I415" s="5" t="n">
+        <v>1.531</v>
       </c>
       <c r="J415" t="inlineStr">
         <is>
@@ -46717,28 +46761,28 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligation (note 6)</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr"/>
+          <t>Management fee (note 8)</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E416" s="5" t="n">
-        <v>0.333</v>
+        <v>2.018</v>
       </c>
       <c r="F416" s="5" t="n">
-        <v>0.352</v>
+        <v>3.016</v>
       </c>
       <c r="G416" s="5" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.401</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="I416" s="5" t="n">
+        <v>4.495</v>
       </c>
       <c r="J416" t="inlineStr">
         <is>
@@ -46804,12 +46848,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Income and capital taxes</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Income and capital taxes (note 11)</t>
+          <t>Current expense (note 10)</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -46818,21 +46862,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F417" s="5" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="G417" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H417" s="5" t="n">
+        <v>27.792</v>
+      </c>
+      <c r="I417" s="5" t="n">
+        <v>23.558</v>
       </c>
       <c r="J417" t="inlineStr">
         <is>
@@ -46898,39 +46942,35 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Income and capital taxes</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (note 11)</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Deferred recovery (note 10)</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F418" s="5" t="n">
-        <v>6.344</v>
-      </c>
-      <c r="G418" s="5" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H418" s="5" t="n">
+        <v>-9.175000000000001</v>
+      </c>
+      <c r="I418" s="5" t="n">
+        <v>-3.552</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -46996,28 +47036,30 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Income and capital taxes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Income and capital taxes total</t>
+          <t>Accretion of asset retirement obligation (note 7)</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
-      <c r="E419" s="5" t="n">
-        <v>-5.083</v>
-      </c>
-      <c r="F419" s="5" t="n">
-        <v>6.62</v>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G419" s="5" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.344</v>
+      </c>
+      <c r="H419" s="5" t="n">
+        <v>0.381</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -47088,34 +47130,30 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Income and capital taxes</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income $</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Current expense (note 11)</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F420" s="5" t="n">
-        <v>49.349</v>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G420" s="5" t="n">
-        <v>55.259</v>
-      </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08</v>
+      </c>
+      <c r="H420" s="5" t="n">
+        <v>27.792</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -47186,32 +47224,30 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Income and capital taxes</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Net income per share, basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E421" s="5" t="n">
-        <v>6.3e-07</v>
-      </c>
-      <c r="F421" s="5" t="n">
-        <v>8.5e-07</v>
+          <t>Deferred expense (recovery) (note 11)</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G421" s="5" t="n">
-        <v>9.200000000000001e-07</v>
-      </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20.47</v>
+      </c>
+      <c r="H421" s="5" t="n">
+        <v>-9.175000000000001</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -47287,24 +47323,18 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Other income/expense (note 11)</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Royalty expense and mineral tax</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
       <c r="E422" s="5" t="n">
-        <v>2.122</v>
+        <v>-2.733</v>
       </c>
       <c r="F422" s="5" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.092</v>
+      </c>
+      <c r="G422" s="5" t="n">
+        <v>-4.197</v>
       </c>
       <c r="H422" t="inlineStr">
         <is>
@@ -47380,20 +47410,26 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Income and capital taxes</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Income and capital taxes (note 10)</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
-      <c r="E423" s="5" t="n">
-        <v>0.255</v>
+          <t>Other expense (note 10)</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F423" s="5" t="n">
-        <v>0.276</v>
+        <v>-1.85</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
@@ -47474,25 +47510,23 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Income and capital taxes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Future income tax reduction (note 10)</t>
+          <t>Accretion of asset retirement obligation (note 6)</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
       <c r="E424" s="5" t="n">
-        <v>-5.338</v>
+        <v>0.333</v>
       </c>
       <c r="F424" s="5" t="n">
-        <v>-2.057</v>
-      </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.352</v>
+      </c>
+      <c r="G424" s="5" t="n">
+        <v>0.344</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
@@ -47573,24 +47607,20 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E425" s="5" t="n">
-        <v>31.741</v>
+          <t>Income and capital taxes (note 11)</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F425" s="5" t="n">
-        <v>36.273</v>
-      </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.276</v>
+      </c>
+      <c r="G425" s="5" t="n">
+        <v>0.08</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
@@ -47671,20 +47701,24 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Deficit, beginning of year</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
-      <c r="E426" s="5" t="n">
-        <v>-348.027</v>
+          <t>Deferred income tax expense (note 11)</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F426" s="5" t="n">
-        <v>-386.766</v>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.344</v>
+      </c>
+      <c r="G426" s="5" t="n">
+        <v>20.47</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
@@ -47765,20 +47799,18 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Distributions declared</t>
+          <t>Income and capital taxes total</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
       <c r="E427" s="5" t="n">
-        <v>-70.48</v>
+        <v>-5.083</v>
       </c>
       <c r="F427" s="5" t="n">
-        <v>-98.11499999999999</v>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.62</v>
+      </c>
+      <c r="G427" s="5" t="n">
+        <v>20.55</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
@@ -47859,22 +47891,24 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Elimination of deficit in accordance with the Reorganization (note 7)</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr"/>
+          <t>Net income and comprehensive income $</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F428" s="5" t="n">
-        <v>448.608</v>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>49.349</v>
+      </c>
+      <c r="G428" s="5" t="n">
+        <v>55.259</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
@@ -47955,84 +47989,848 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
+          <t>Net income per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E429" s="5" t="n">
+        <v>6.3e-07</v>
+      </c>
+      <c r="F429" s="5" t="n">
+        <v>8.5e-07</v>
+      </c>
+      <c r="G429" s="5" t="n">
+        <v>9.200000000000001e-07</v>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Other income/expense (note 11)</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E430" s="5" t="n">
+        <v>2.122</v>
+      </c>
+      <c r="F430" s="5" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Income and capital taxes</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Income and capital taxes (note 10)</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" s="5" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="F431" s="5" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Income and capital taxes</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Future income tax reduction (note 10)</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" s="5" t="n">
+        <v>-5.338</v>
+      </c>
+      <c r="F432" s="5" t="n">
+        <v>-2.057</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Income and capital taxes</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Net income and comprehensive income</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E433" s="5" t="n">
+        <v>31.741</v>
+      </c>
+      <c r="F433" s="5" t="n">
+        <v>36.273</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Income and capital taxes</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" s="5" t="n">
+        <v>-348.027</v>
+      </c>
+      <c r="F434" s="5" t="n">
+        <v>-386.766</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Income and capital taxes</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Distributions declared</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" s="5" t="n">
+        <v>-70.48</v>
+      </c>
+      <c r="F435" s="5" t="n">
+        <v>-98.11499999999999</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Income and capital taxes</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Elimination of deficit in accordance with the Reorganization (note 7)</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F436" s="5" t="n">
+        <v>448.608</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Income and capital taxes</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
           <t>Deficit, end of year $</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
-      <c r="E429" s="5" t="n">
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" s="5" t="n">
         <v>-386.766</v>
       </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T429" t="inlineStr">
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
         <is>
           <t>-</t>
         </is>
